--- a/artfynd/A 62278-2025 artfynd.xlsx
+++ b/artfynd/A 62278-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,37 +1166,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96940257</v>
+        <v>137441676</v>
       </c>
       <c r="B6" t="n">
-        <v>99754</v>
+        <v>99431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222295</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1204,16 +1204,17 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ambricka, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633174</v>
+        <v>633400</v>
       </c>
       <c r="R6" t="n">
-        <v>6710639</v>
+        <v>6710647</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,12 +1241,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,27 +1271,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Lennart Gårdman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Lennart Gårdman, Anton Gårdman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96940257</t>
+          <t>https://artportalen.se/Sighting/137441676</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81678843</v>
+        <v>96940257</v>
       </c>
       <c r="B7" t="n">
-        <v>103695</v>
+        <v>99754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,19 +1299,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224412</v>
+        <v>222295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hårig sandviol</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Viola rupestris var. rupestris</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>5</t>
@@ -1313,14 +1328,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ambricka, KLG, Upl</t>
+          <t>Ambricka, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633176</v>
+        <v>633174</v>
       </c>
       <c r="R7" t="n">
-        <v>6710636</v>
+        <v>6710639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,12 +1362,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,6 +1392,113 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940257</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>81678843</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ambricka, KLG, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>633176</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6710636</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-05-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-05-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/81678843</t>
         </is>
@@ -1390,6 +1512,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62278-2025 artfynd.xlsx
+++ b/artfynd/A 62278-2025 artfynd.xlsx
@@ -1169,7 +1169,7 @@
         <v>137441676</v>
       </c>
       <c r="B6" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62278-2025 artfynd.xlsx
+++ b/artfynd/A 62278-2025 artfynd.xlsx
@@ -1169,7 +1169,7 @@
         <v>137441676</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
